--- a/documentation/source_to_target_mapping.xlsx
+++ b/documentation/source_to_target_mapping.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="stg_shipment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="phase2_derivation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1539,4 +1540,502 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>target_table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>derivation_rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dim_location</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PUBLIC/DERIVED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Origins from manufacturing_site; destinations one DC per destination_country; warehouse locations simulated. Coordinates left NULL (never fabricated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dim_location_xref</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Preserves each raw location string and how it mapped to a location_id (match_method).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dim_hts_code</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>One illustrative HS-prefixed code per product category. NOT official US HTS (code_type).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dim_product</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5 SKUs per renewable-energy category; unit_weight/value seeded from the observed per-unit source distribution (median of weight/qty, value/qty).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dim_business_partner</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DERIVED/SIMULATED</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unified registry: suppliers (real vendors), carriers, brokers, customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dim_supplier</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>One per real source vendor; location = most-used manufacturing site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dim_warehouse</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5 regional DCs (config); location FK to dim_location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dim_carrier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12 fictional carriers across all modes (config).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dim_lane</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Distinct (origin, destination, mode) combinations; standard_transit_days = mode/region standard (source has no departure timestamp). estimated_distance NULL (not measurable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dim_rate_card</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>One rate per (pool carrier, lane); rate_per_kg ~ observed mode freight/kg with deterministic carrier spread; single wide effective window (no overlap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fact_purchase_order</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Groups shipment lines sharing a source PO reference; else one derived PO per line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fact_shipment</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>One per staged shipment (source_record_id lineage). Real value/qty/delivery preserved; ship dates derived from mode/lane transit (ship_date_derived_flag=1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fact_shipment_milestone</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mode-aware milestone templates; timestamps reconcile to shipment dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fact_freight_invoice</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>One per delivered shipment; charges from the applicable rate card (+small rating noise within audit tolerance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fact_invoice_line</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BASE_FREIGHT / FUEL_SURCHARGE / ACCESSORIAL / TAX lines; sum to total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fact_accessorial_charge</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Low-frequency, mode-plausible charges; clean baseline all contractually allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fact_proof_of_delivery</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>One per delivered shipment; generic role-based recipient (no PII).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fact_claim</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Risk-weighted legitimate claims (late/high-value/ocean more likely).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fact_carrier_capacity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Monthly per carrier x lane; utilization &lt;=100% with seasonal variation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fact_invoice_approval</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4-stage workflow; chronological; paid =&gt; approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fact_accrual</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Per shipment by accounting period; expected freight vs received invoice; RELEASED only when invoice received &amp; approved.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>